--- a/artifacts/evidence/exports/browser.xlsx
+++ b/artifacts/evidence/exports/browser.xlsx
@@ -97,562 +97,634 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Catalog source 0</t>
+          <t>A long wrapped anchor with several lines of visible text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>http://127.0.0.1:52478/catalog/0</t>
+          <t>http://127.0.0.1:52478/wrapped</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Catalog source 1</t>
+          <t>=SUM(1,2)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>http://127.0.0.1:52478/catalog/1</t>
+          <t>http://127.0.0.1:52478/formula?value=(literal)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Catalog source 2</t>
+          <t>&lt;img src=x onerror=alert(1)&gt;</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>http://127.0.0.1:52478/catalog/2</t>
+          <t>http://127.0.0.1:52478/html</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Catalog source 15</t>
+          <t>Email the research team</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>http://127.0.0.1:52478/catalog/15</t>
+          <t>mailto:research@example.org</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Catalog source 16</t>
+          <t>Call the lab</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>http://127.0.0.1:52478/catalog/16</t>
+          <t>tel:+15550123</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Catalog source 17</t>
+          <t>Open shadow source</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>http://127.0.0.1:52478/catalog/17</t>
+          <t>http://127.0.0.1:52478/shadow</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Attention in small systems</t>
+          <t>Catalog source 0</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>http://127.0.0.1:52478/papers/attention.pdf</t>
+          <t>http://127.0.0.1:52478/catalog/0</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Geometry, “frames” &amp; 雪</t>
+          <t>Catalog source 1</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>http://127.0.0.1:52478/papers/geometry.pdf?edition=2</t>
+          <t>http://127.0.0.1:52478/catalog/1</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Download PDF</t>
+          <t>Catalog source 2</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>http://127.0.0.1:52478/papers/attention.pdf</t>
+          <t>http://127.0.0.1:52478/catalog/2</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t/>
+          <t>Catalog source 15</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>http://127.0.0.1:52478/appendix</t>
+          <t>http://127.0.0.1:52478/catalog/15</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Visible label</t>
+          <t>Catalog source 16</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>http://127.0.0.1:52478/visible</t>
+          <t>http://127.0.0.1:52478/catalog/16</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Atlas notebook — field edition</t>
+          <t>Catalog source 17</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>http://127.0.0.1:52478/products/atlas</t>
+          <t>http://127.0.0.1:52478/catalog/17</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Open-sky telescope</t>
+          <t>Attention in small systems</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>https://example.org/telescope</t>
+          <t>http://127.0.0.1:52478/papers/attention.pdf</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>OBS-42</t>
+          <t>Geometry, “frames” &amp; 雪</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>http://127.0.0.1:52478/tickets/42</t>
+          <t>http://127.0.0.1:52478/papers/geometry.pdf?edition=2</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>OBS-43</t>
+          <t>Download PDF</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>http://127.0.0.1:52478/tickets/43</t>
+          <t>http://127.0.0.1:52478/papers/attention.pdf</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A long wrapped anchor with several lines of visible text</t>
+          <t/>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>http://127.0.0.1:52478/wrapped</t>
+          <t>http://127.0.0.1:52478/appendix</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>=SUM(1,2)</t>
+          <t>Visible label</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>http://127.0.0.1:52478/formula?value=(literal)</t>
+          <t>http://127.0.0.1:52478/visible</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>&lt;img src=x onerror=alert(1)&gt;</t>
+          <t>Atlas notebook — field edition</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>http://127.0.0.1:52478/html</t>
+          <t>http://127.0.0.1:52478/products/atlas</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Email the research team</t>
+          <t>Open-sky telescope</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>mailto:research@example.org</t>
+          <t>https://example.org/telescope</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Call the lab</t>
+          <t>OBS-42</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>tel:+15550123</t>
+          <t>http://127.0.0.1:52478/tickets/42</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Open shadow source</t>
+          <t>OBS-43</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>http://127.0.0.1:52478/shadow</t>
+          <t>http://127.0.0.1:52478/tickets/43</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Loaded after the page</t>
+          <t>A long wrapped anchor with several lines of visible text</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>http://127.0.0.1:52478/dynamic</t>
+          <t>http://127.0.0.1:52478/wrapped</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Catalog source 0</t>
+          <t>=SUM(1,2)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>http://127.0.0.1:52478/catalog/0</t>
+          <t>http://127.0.0.1:52478/formula?value=(literal)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Catalog source 1</t>
+          <t>&lt;img src=x onerror=alert(1)&gt;</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>http://127.0.0.1:52478/catalog/1</t>
+          <t>http://127.0.0.1:52478/html</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Catalog source 2</t>
+          <t>Email the research team</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>http://127.0.0.1:52478/catalog/2</t>
+          <t>mailto:research@example.org</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Catalog source 3</t>
+          <t>Call the lab</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>http://127.0.0.1:52478/catalog/3</t>
+          <t>tel:+15550123</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Catalog source 4</t>
+          <t>Open shadow source</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>http://127.0.0.1:52478/catalog/4</t>
+          <t>http://127.0.0.1:52478/shadow</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Catalog source 5</t>
+          <t>Loaded after the page</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>http://127.0.0.1:52478/catalog/5</t>
+          <t>http://127.0.0.1:52478/dynamic</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Catalog source 6</t>
+          <t>Catalog source 0</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>http://127.0.0.1:52478/catalog/6</t>
+          <t>http://127.0.0.1:52478/catalog/0</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Catalog source 7</t>
+          <t>Catalog source 1</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>http://127.0.0.1:52478/catalog/7</t>
+          <t>http://127.0.0.1:52478/catalog/1</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Catalog source 8</t>
+          <t>Catalog source 2</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>http://127.0.0.1:52478/catalog/8</t>
+          <t>http://127.0.0.1:52478/catalog/2</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Catalog source 9</t>
+          <t>Catalog source 3</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>http://127.0.0.1:52478/catalog/9</t>
+          <t>http://127.0.0.1:52478/catalog/3</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Catalog source 10</t>
+          <t>Catalog source 4</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>http://127.0.0.1:52478/catalog/10</t>
+          <t>http://127.0.0.1:52478/catalog/4</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Catalog source 11</t>
+          <t>Catalog source 5</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>http://127.0.0.1:52478/catalog/11</t>
+          <t>http://127.0.0.1:52478/catalog/5</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Catalog source 12</t>
+          <t>Catalog source 6</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>http://127.0.0.1:52478/catalog/12</t>
+          <t>http://127.0.0.1:52478/catalog/6</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Catalog source 13</t>
+          <t>Catalog source 7</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>http://127.0.0.1:52478/catalog/13</t>
+          <t>http://127.0.0.1:52478/catalog/7</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Catalog source 14</t>
+          <t>Catalog source 8</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>http://127.0.0.1:52478/catalog/14</t>
+          <t>http://127.0.0.1:52478/catalog/8</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Catalog source 15</t>
+          <t>Catalog source 9</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>http://127.0.0.1:52478/catalog/15</t>
+          <t>http://127.0.0.1:52478/catalog/9</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Catalog source 16</t>
+          <t>Catalog source 10</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>http://127.0.0.1:52478/catalog/16</t>
+          <t>http://127.0.0.1:52478/catalog/10</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Catalog source 17</t>
+          <t>Catalog source 11</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>http://127.0.0.1:52478/catalog/17</t>
+          <t>http://127.0.0.1:52478/catalog/11</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Catalog source 18</t>
+          <t>Catalog source 12</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>http://127.0.0.1:52478/catalog/18</t>
+          <t>http://127.0.0.1:52478/catalog/12</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Catalog source 19</t>
+          <t>Catalog source 13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>http://127.0.0.1:52478/catalog/19</t>
+          <t>http://127.0.0.1:52478/catalog/13</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Source inside a frame</t>
+          <t>Catalog source 14</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>http://127.0.0.1:52478/frame-source</t>
+          <t>http://127.0.0.1:52478/catalog/14</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>The final source</t>
+          <t>Catalog source 15</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>http://127.0.0.1:52478/bottom</t>
+          <t>http://127.0.0.1:52478/catalog/15</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Catalog source 16</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>http://127.0.0.1:52478/normal</t>
+          <t>http://127.0.0.1:52478/catalog/16</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Email subject</t>
+          <t>Catalog source 17</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>mailto:?subject=Hello</t>
+          <t>http://127.0.0.1:52478/catalog/17</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>Catalog source 18</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>http://127.0.0.1:52478/catalog/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Catalog source 19</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>http://127.0.0.1:52478/catalog/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Source inside a frame</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>http://127.0.0.1:52478/frame-source</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>The final source</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>http://127.0.0.1:52478/bottom</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>http://127.0.0.1:52478/normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Email subject</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>mailto:?subject=Hello</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
           <t>Compose email</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B60" t="inlineStr">
         <is>
           <t>mailto:</t>
         </is>
